--- a/ru/downloads/data-excel/2.c.1.1.xlsx
+++ b/ru/downloads/data-excel/2.c.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984239F9-D93C-4350-861F-24CC32DA1BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14280" windowHeight="11760"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ИПЦ  2" sheetId="1" r:id="rId1"/>
@@ -20,14 +21,6 @@
     <definedName name="Button_2">"Pokreal_CHC_List"</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -142,30 +135,38 @@
     <t>(өткөн жылдын декабрына карата пайыз менен)</t>
   </si>
   <si>
-    <t>2.с.1.1b Индекс потребительских цен на продовольственные товары по Кыргызской Республике</t>
-  </si>
-  <si>
-    <t>2.с1.1b Кыргыз Республикасы боюнча азык-түлүк товарларына болгон керектөө бааларынын индекси</t>
-  </si>
-  <si>
-    <t>2.c.1.1b Consumer price index for food products in the Kyrgyz Republic</t>
+    <t>2.с.1.1 Индекс потребительских цен на продовольственные товары по Кыргызской Республике и областям</t>
+  </si>
+  <si>
+    <t>2.с1.1 Кыргыз Республикасы жана облустар боюнча азык-түлүк товарларына болгон керектөө бааларынын индекси</t>
+  </si>
+  <si>
+    <t>2.c.1.1 Consumer price index for food products in the Kyrgyz Republic and oblasts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _р_._-;\-* #,##0.00\ _р_._-;_-* &quot;-&quot;??\ _р_._-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -332,148 +333,160 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="24">
+  <cellStyleXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="33">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="29">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="23" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="23" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="24">
-    <cellStyle name="Normal 17" xfId="20"/>
-    <cellStyle name="Normal 2" xfId="22"/>
+  <cellStyles count="25">
+    <cellStyle name="Normal 17" xfId="20" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="24" xr:uid="{9BFBF263-22D0-46D8-84FF-12E1220402F5}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="4"/>
-    <cellStyle name="Обычный 11" xfId="23"/>
-    <cellStyle name="Обычный 2" xfId="5"/>
-    <cellStyle name="Обычный 2 2" xfId="6"/>
-    <cellStyle name="Обычный 2 3" xfId="7"/>
-    <cellStyle name="Обычный 3" xfId="8"/>
-    <cellStyle name="Обычный 3 2" xfId="9"/>
-    <cellStyle name="Обычный 4" xfId="10"/>
-    <cellStyle name="Обычный 5" xfId="11"/>
-    <cellStyle name="Обычный 6" xfId="3"/>
-    <cellStyle name="Обычный 7" xfId="21"/>
-    <cellStyle name="Обычный 8" xfId="12"/>
-    <cellStyle name="Обычный 9" xfId="13"/>
-    <cellStyle name="Обычный_80102" xfId="1"/>
-    <cellStyle name="Обычный_stand (3)" xfId="2"/>
-    <cellStyle name="Пояснение 2" xfId="14"/>
-    <cellStyle name="Процентный 2" xfId="15"/>
-    <cellStyle name="Процентный 3" xfId="16"/>
-    <cellStyle name="Стиль 1" xfId="17"/>
-    <cellStyle name="Финансовый 2" xfId="18"/>
-    <cellStyle name="Финансовый 3" xfId="19"/>
+    <cellStyle name="Обычный 10" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 11" xfId="23" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 2 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 3" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 4" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 5" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Обычный 7" xfId="21" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Обычный 8" xfId="12" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Обычный 9" xfId="13" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Обычный_80102" xfId="1" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Обычный_stand (3)" xfId="2" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Пояснение 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Процентный 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Процентный 3" xfId="16" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Стиль 1" xfId="17" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Финансовый 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Финансовый 3" xfId="19" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -774,8 +787,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="3" width="37.5703125" style="4" customWidth="1"/>
@@ -783,166 +796,173 @@
     <col min="21" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" customHeight="1">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:21" ht="45" customHeight="1">
+      <c r="A1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="17" t="s">
         <v>38</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1">
-      <c r="A2" s="24" t="s">
+    <row r="2" spans="1:21" ht="18" customHeight="1">
+      <c r="A2" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>34</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1">
+    <row r="3" spans="1:21" ht="15" customHeight="1" thickBot="1">
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="1"/>
       <c r="E3" s="3"/>
       <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:20" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="11" t="s">
+      <c r="U3" s="27"/>
+    </row>
+    <row r="4" spans="1:21" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>2007</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>2008</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>2009</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>2010</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>2011</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <v>2012</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <v>2013</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="12">
         <v>2014</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <v>2015</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <v>2016</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="12">
         <v>2017</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="12">
         <v>2018</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="12">
         <v>2019</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="12">
         <v>2020</v>
       </c>
-      <c r="R4" s="13">
+      <c r="R4" s="12">
         <v>2021</v>
       </c>
-      <c r="S4" s="13">
+      <c r="S4" s="12">
         <v>2022</v>
       </c>
-      <c r="T4" s="13">
+      <c r="T4" s="12">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="14.25" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="U4" s="30">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="14.25" customHeight="1">
+      <c r="A5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="21">
         <v>131.54715835747666</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="21">
         <v>120.91338718808116</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="21">
         <v>92.628334783839932</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="21">
         <v>127.01999499304641</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="21">
         <v>103.48574603932104</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="21">
         <v>104.49447433808045</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="21">
         <v>101.76960163599213</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="21">
         <v>113.85708071378342</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="21">
         <v>95.79497627095887</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="21">
         <v>94.980193620007185</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="21">
         <v>102.7133320487825</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="21">
         <v>97.394314160825076</v>
       </c>
-      <c r="P5" s="23">
+      <c r="P5" s="21">
         <v>105.74483114760656</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="21">
         <v>117.60684979252385</v>
       </c>
-      <c r="R5" s="23">
+      <c r="R5" s="21">
         <v>113.34848864817617</v>
       </c>
-      <c r="S5" s="25">
+      <c r="S5" s="23">
         <v>115.8</v>
       </c>
-      <c r="T5" s="26">
+      <c r="T5" s="24">
         <v>103.3752971770694</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="14.25" customHeight="1">
+      <c r="U5" s="31">
+        <v>105.37535351292098</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="14.25" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -1000,18 +1020,21 @@
       <c r="S6" s="4">
         <v>115.2</v>
       </c>
-      <c r="T6" s="27">
+      <c r="T6" s="25">
         <v>104.28289267885566</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="14.25" customHeight="1">
+      <c r="U6" s="32">
+        <v>103.80658955951687</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="14.25" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="6">
@@ -1062,18 +1085,21 @@
       <c r="S7" s="4">
         <v>115.4</v>
       </c>
-      <c r="T7" s="27">
+      <c r="T7" s="25">
         <v>105.54952929965596</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="14.25" customHeight="1">
+      <c r="U7" s="28">
+        <v>103.42779773925503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="14.25" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="6">
@@ -1124,18 +1150,21 @@
       <c r="S8" s="4">
         <v>111.8</v>
       </c>
-      <c r="T8" s="27">
+      <c r="T8" s="25">
         <v>103.51673393645765</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="14.25" customHeight="1">
+      <c r="U8" s="28">
+        <v>105.14466865023367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="14.25" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="6">
@@ -1186,18 +1215,21 @@
       <c r="S9" s="4">
         <v>116.8</v>
       </c>
-      <c r="T9" s="27">
+      <c r="T9" s="25">
         <v>106.47711005273266</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="14.25" customHeight="1">
+      <c r="U9" s="28">
+        <v>103.42652324624606</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="6">
@@ -1248,18 +1280,21 @@
       <c r="S10" s="4">
         <v>108.2</v>
       </c>
-      <c r="T10" s="27">
+      <c r="T10" s="25">
         <v>107.06485907396235</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="14.25" customHeight="1">
+      <c r="U10" s="28">
+        <v>103.90565426731339</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="14.25" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="6">
@@ -1310,18 +1345,21 @@
       <c r="S11" s="4">
         <v>111</v>
       </c>
-      <c r="T11" s="27">
+      <c r="T11" s="25">
         <v>109.45786616400459</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="14.25" customHeight="1">
+      <c r="U11" s="28">
+        <v>100.07295707197417</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.25" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="6">
@@ -1372,18 +1410,21 @@
       <c r="S12" s="4">
         <v>115.8</v>
       </c>
-      <c r="T12" s="27">
+      <c r="T12" s="25">
         <v>101.11876601355125</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="14.25" customHeight="1">
+      <c r="U12" s="28">
+        <v>102.22206049215099</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="14.25" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="6">
@@ -1419,114 +1460,120 @@
       <c r="N13" s="6">
         <v>101.5783662149571</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <v>97.346546082576666</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="8">
         <v>105.61571039117108</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="Q13" s="8">
         <v>118.87059844457349</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="8">
         <v>112.69493421065988</v>
       </c>
       <c r="S13" s="4">
         <v>117.9</v>
       </c>
-      <c r="T13" s="27">
+      <c r="T13" s="25">
         <v>102.74015470892634</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A14" s="17" t="s">
+      <c r="U13" s="28">
+        <v>106.66797685043008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A14" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="16">
         <v>130.50325093984162</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="16">
         <v>132.38912904966173</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="16">
         <v>91.207604037247833</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="16">
         <v>133.71497550164167</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="16">
         <v>103.63552186450886</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="16">
         <v>106.98518807336717</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="16">
         <v>104.55440021461374</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="16">
         <v>118.55329806082315</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="16">
         <v>93.999692152661922</v>
       </c>
-      <c r="M14" s="18">
+      <c r="M14" s="16">
         <v>94.9145365038829</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="16">
         <v>103.95698983548682</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="9">
         <v>98.011360962978884</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="9">
         <v>102.47048806260071</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="9">
         <v>114.06377070452145</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="9">
         <v>113.95067699644588</v>
       </c>
-      <c r="S14" s="10">
+      <c r="S14" s="9">
         <v>112.4</v>
       </c>
-      <c r="T14" s="28">
+      <c r="T14" s="26">
         <v>103.21772010523679</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="12.95" customHeight="1"/>
-    <row r="16" spans="1:20">
-      <c r="B16" s="21"/>
+      <c r="U14" s="29">
+        <v>105.35839071525159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="12.95" customHeight="1"/>
+    <row r="16" spans="1:21">
+      <c r="B16" s="19"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="22"/>
+      <c r="B17" s="20"/>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="22"/>
+      <c r="B18" s="20"/>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="22"/>
+      <c r="B19" s="20"/>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="22"/>
+      <c r="B20" s="20"/>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="22"/>
+      <c r="B21" s="20"/>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="22"/>
+      <c r="B22" s="20"/>
     </row>
     <row r="23" spans="2:2">
-      <c r="B23" s="22"/>
+      <c r="B23" s="20"/>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" s="21"/>
+      <c r="B24" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.51181102362204722" footer="0.51181102362204722"/>
